--- a/.claude/skills/daily-agenda/state/activity-log.xlsx
+++ b/.claude/skills/daily-agenda/state/activity-log.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>יתגלגל למחר; הודעת וואטסאפ מוכנה ביומן</t>
+          <t>יתגלגל למחר</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,11 @@
           <t>לא בוצע</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>סוכם היום; נשאר לקרוא פסק הרש"פ במלואו</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -589,7 +593,11 @@
           <t>לא בוצע</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>סוכם היום</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -617,7 +625,11 @@
           <t>לא בוצע</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>סוכם היום</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -642,7 +654,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>לא בוצע</t>
+          <t>בוצע</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>

--- a/.claude/skills/daily-agenda/state/activity-log.xlsx
+++ b/.claude/skills/daily-agenda/state/activity-log.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -691,6 +691,686 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>📞 פנייה לאבי ממן (פאוור גרופ) — פגישת 15 דק'</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Vercel — התראת התחברות חדשה (לוודא שזה אתה)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>יומן</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>🪑 לחפש את כסא הים הסגול שאבד</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>מייל</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>🔴 ביטוח לאומי — מכתב דרישת מידע באתר השירות האישי</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>מייל</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vercel — כשל בדיפלוי preview לפרויקט crm</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>💍 חתונה — בת של דוד ישראל (שלישי 28/07)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>אירוע מחר</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>📄 לעבור על מכתב מיצוי הליכים (שמבי)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>📘 להמשיך לטפל בחוברת</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>💳 לשלם שכר לימוד — תואר מנהל עסקים</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>🧾 להכין מסמכים לרואה חשבון</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>🧾 להוציא קבלות</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>🔑 לשכפל מפתחות</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>💰 לגבות כסף מאופק ומיניב</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>🏦 לשלוח פרטי חשבון לאריאל כהן</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>📞 שיחה עם יופיקס — מסמכי הסמכה של רחל נחמני</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>🧾 קבלות מד"ר שכטר לביטוח לאומי להחזר</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>🏠 ביקור שמאי בבית — שלישי 10:00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>אירוע מחר</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>👩‍💼 לדבר עם חדוה על ביקור השמאי</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>🖨️ דפוס צבאן — כרטיסי ביקור לנאור</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>🔎 לבדוק היכן ההפרשות של מיכל</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>🏗️ בדיקת תביעה על ליקויי בנייה — מוטי קרויזר</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>יום שני</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>חותם</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>🖥️ זום "משימות חותם" — שלישי 08:30</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>אירוע מחר</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.claude/skills/daily-agenda/state/activity-log.xlsx
+++ b/.claude/skills/daily-agenda/state/activity-log.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -749,7 +749,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -809,7 +808,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -837,7 +835,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -897,7 +894,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1149,7 +1145,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1241,7 +1236,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1370,6 +1364,202 @@
           <t>אירוע מחר</t>
         </is>
       </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>יום רביעי</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>💍 חתונה — בת של דוד ישראל</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>יום רביעי</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>🔑 לשכפל מפתחות</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>יום רביעי</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>🧾 קבלות מד"ר שכטר לביטוח לאומי להחזר</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>יום רביעי</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>🏠 ביקור שמאי בבית</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>יום רביעי</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>🖨️ דפוס צבאן — כרטיסי ביקור לנאור</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>יום רביעי</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>🏗️ בדיקת תביעה על ליקויי בנייה — מוטי קרויזר</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>יום רביעי</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>חותם</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>🖥️ זום "משימות חותם"</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/.claude/skills/daily-agenda/state/activity-log.xlsx
+++ b/.claude/skills/daily-agenda/state/activity-log.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1391,7 +1391,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1419,7 +1418,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1447,7 +1445,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1475,7 +1472,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1503,7 +1499,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1531,7 +1526,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1559,7 +1553,426 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>📞 פנייה לאבי ממן (פאוור גרופ)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>🪑 כסא הים הסגול שאבד</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>📘 להמשיך לטפל בחוברת</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>💳 לשלם שכר לימוד — תואר מנהל עסקים</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>🧾 להכין מסמכים לרואה חשבון</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>🧾 להוציא קבלות</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>💰 לגבות כסף מאופק ומיניב</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>🏦 לשלוח פרטי חשבון לאריאל כהן</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>🔎 לבדוק היכן ההפרשות של מיכל</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>מייל</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>🔴 מיטב — חוב מעסיק / הפקדות חסרות (CRM365)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>🔁 סקירה שבועית עו"ד (אביאור, חדוה, שוהם, טל)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>📞 טל שרת — לדבר עם רבקה משה</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>מייל</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>🎓 אונו — חידוש התאמות למבחנים (פג בעוד ~3 חודשים)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>מתגלגל, לא דחוף</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>יום ראשון</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>🏘️ לדבר עם מתווך נדל"ן אלקבץ תרי"ג, לתאם פגישה</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/.claude/skills/daily-agenda/state/activity-log.xlsx
+++ b/.claude/skills/daily-agenda/state/activity-log.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1612,7 +1612,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1672,7 +1671,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1732,7 +1730,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1760,7 +1757,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1852,7 +1848,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1880,7 +1875,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1908,7 +1902,6 @@
           <t>בוצע</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1969,6 +1962,446 @@
         </is>
       </c>
       <c r="F51" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>📞 פנייה לאבי ממן (פאוור גרופ)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>📘 להמשיך לטפל בחוברת</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>🧾 להכין מסמכים לרואה חשבון</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>🏦 לשלוח פרטי חשבון לאריאל כהן</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>🔎 לבדוק היכן ההפרשות של מיכל</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>🎓 אונו — חידוש התאמות למבחנים</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>🏘️ מתווך נדל"ן אלקבץ תרי"ג — לתאם פגישה</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>מייל</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>🔴 ביטוח לאומי — תשובה לפנייה 15697342 (נפגעי פעולות איבה)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>מייל</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>🏥 כללית — בירור מול המרפאה (08-9937777)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>👩‍💼 לוודא עם חדווה מה עם השמאי</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>בוצע</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>🔁 סקירה שבועית עו"ד (אביאור, חדוה, שוהם, טל)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>📄 חוזה אלעזר אפללו — מכירה</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>משימה</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>💸 חוב לאיתמר נגר — 100 ₪</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>מתגלגל</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>יום חמישי</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>חותם</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>🖥️ למלא שקופית חותם</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>לא בוצע</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>מתגלגל</t>
         </is>
